--- a/Result/profitability/3019.xlsx
+++ b/Result/profitability/3019.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.05</v>
       </c>
       <c r="M2" t="n">
-        <v>1.42375</v>
+        <v>1.3575</v>
       </c>
       <c r="N2" t="n">
-        <v>17.545</v>
+        <v>17.15</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.87</v>
       </c>
       <c r="M3" t="n">
-        <v>1.22625</v>
+        <v>1.29875</v>
       </c>
       <c r="N3" t="n">
-        <v>16.31625</v>
+        <v>16.3025</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>1.33375</v>
+        <v>1.475</v>
       </c>
       <c r="N4" t="n">
-        <v>15.1125</v>
+        <v>15.27</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.98</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3575</v>
+        <v>1.24</v>
       </c>
       <c r="N5" t="n">
-        <v>14.20625</v>
+        <v>14.005</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8724999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="N6" t="n">
-        <v>12.01625</v>
+        <v>11.56375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5700000000000001</v>
+        <v>0.6737500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>10.3725</v>
+        <v>10.73</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.61</v>
       </c>
       <c r="M8" t="n">
-        <v>0.51</v>
+        <v>0.61875</v>
       </c>
       <c r="N8" t="n">
-        <v>10.1425</v>
+        <v>10.27875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3019</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>8028</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6552</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1477</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="G75" t="n">
+        <v>807</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.05%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" t="n">
+        <v>815</v>
+      </c>
+      <c r="K75" t="n">
+        <v>537</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.80125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.8699999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.8285714285714285</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.06300578034682069</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3286713286713286</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.609999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.08050000000000002</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
